--- a/ig/DM-SIDOBA/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-TRE-R66-CategorieEtablissement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="712">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -793,7 +793,10 @@
     <t>236</t>
   </si>
   <si>
-    <t>Centre Placement Familial Socio-Educatif (C.P.F.S.E.)</t>
+    <t>Service de placement familial</t>
+  </si>
+  <si>
+    <t>Le placement familial est, au sens strict du terme, un dispositif qui permet de prendre en charge un enfant dans une autre famille que la sienne, afin de résoudre une situation de danger le concernant. Remarque : Suite à une réunion avec l'ASE (DGCS), il a été décidé que le changement de nom de la catégorie Centre Placement Familial Socio-Educatif (C.P.F.S.E.)  en « Service de placement familial» (catégorie 236).</t>
   </si>
   <si>
     <t>237</t>
@@ -3765,17 +3768,19 @@
       <c r="C100" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="D100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>260</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -3784,10 +3789,10 @@
         <v>61</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -3796,10 +3801,10 @@
         <v>61</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -3808,10 +3813,10 @@
         <v>61</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -3820,10 +3825,10 @@
         <v>61</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -3832,10 +3837,10 @@
         <v>61</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -3844,10 +3849,10 @@
         <v>61</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -3856,10 +3861,10 @@
         <v>61</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -3868,10 +3873,10 @@
         <v>61</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -3880,10 +3885,10 @@
         <v>61</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -3892,10 +3897,10 @@
         <v>61</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -3904,10 +3909,10 @@
         <v>61</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -3916,10 +3921,10 @@
         <v>61</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -3928,10 +3933,10 @@
         <v>61</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -3940,10 +3945,10 @@
         <v>61</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -3952,10 +3957,10 @@
         <v>61</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -3964,10 +3969,10 @@
         <v>61</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -3976,10 +3981,10 @@
         <v>61</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -3988,10 +3993,10 @@
         <v>61</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -4000,10 +4005,10 @@
         <v>61</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -4012,10 +4017,10 @@
         <v>61</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -4024,10 +4029,10 @@
         <v>61</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -4036,10 +4041,10 @@
         <v>61</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -4048,10 +4053,10 @@
         <v>61</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -4060,10 +4065,10 @@
         <v>61</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D125" s="2"/>
     </row>
@@ -4072,10 +4077,10 @@
         <v>61</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D126" s="2"/>
     </row>
@@ -4084,10 +4089,10 @@
         <v>61</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D127" s="2"/>
     </row>
@@ -4096,10 +4101,10 @@
         <v>61</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D128" s="2"/>
     </row>
@@ -4108,10 +4113,10 @@
         <v>61</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D129" s="2"/>
     </row>
@@ -4120,10 +4125,10 @@
         <v>61</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D130" s="2"/>
     </row>
@@ -4132,10 +4137,10 @@
         <v>61</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D131" s="2"/>
     </row>
@@ -4144,10 +4149,10 @@
         <v>61</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D132" s="2"/>
     </row>
@@ -4156,10 +4161,10 @@
         <v>61</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D133" s="2"/>
     </row>
@@ -4168,10 +4173,10 @@
         <v>61</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D134" s="2"/>
     </row>
@@ -4180,10 +4185,10 @@
         <v>61</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D135" s="2"/>
     </row>
@@ -4192,10 +4197,10 @@
         <v>61</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D136" s="2"/>
     </row>
@@ -4204,10 +4209,10 @@
         <v>61</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D137" s="2"/>
     </row>
@@ -4216,10 +4221,10 @@
         <v>61</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D138" s="2"/>
     </row>
@@ -4228,10 +4233,10 @@
         <v>61</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D139" s="2"/>
     </row>
@@ -4240,10 +4245,10 @@
         <v>61</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D140" s="2"/>
     </row>
@@ -4252,10 +4257,10 @@
         <v>61</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D141" s="2"/>
     </row>
@@ -4264,10 +4269,10 @@
         <v>61</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D142" s="2"/>
     </row>
@@ -4276,10 +4281,10 @@
         <v>61</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D143" s="2"/>
     </row>
@@ -4288,10 +4293,10 @@
         <v>61</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D144" s="2"/>
     </row>
@@ -4300,10 +4305,10 @@
         <v>61</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D145" s="2"/>
     </row>
@@ -4312,10 +4317,10 @@
         <v>61</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D146" s="2"/>
     </row>
@@ -4324,10 +4329,10 @@
         <v>61</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D147" s="2"/>
     </row>
@@ -4336,10 +4341,10 @@
         <v>61</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D148" s="2"/>
     </row>
@@ -4348,10 +4353,10 @@
         <v>61</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D149" s="2"/>
     </row>
@@ -4360,10 +4365,10 @@
         <v>61</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D150" s="2"/>
     </row>
@@ -4372,10 +4377,10 @@
         <v>61</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D151" s="2"/>
     </row>
@@ -4384,10 +4389,10 @@
         <v>61</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D152" s="2"/>
     </row>
@@ -4396,10 +4401,10 @@
         <v>61</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D153" s="2"/>
     </row>
@@ -4408,10 +4413,10 @@
         <v>61</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D154" s="2"/>
     </row>
@@ -4420,10 +4425,10 @@
         <v>61</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D155" s="2"/>
     </row>
@@ -4432,10 +4437,10 @@
         <v>61</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D156" s="2"/>
     </row>
@@ -4444,10 +4449,10 @@
         <v>61</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D157" s="2"/>
     </row>
@@ -4456,10 +4461,10 @@
         <v>61</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D158" s="2"/>
     </row>
@@ -4468,10 +4473,10 @@
         <v>61</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D159" s="2"/>
     </row>
@@ -4480,10 +4485,10 @@
         <v>61</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D160" s="2"/>
     </row>
@@ -4492,10 +4497,10 @@
         <v>61</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D161" s="2"/>
     </row>
@@ -4504,10 +4509,10 @@
         <v>61</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D162" s="2"/>
     </row>
@@ -4516,10 +4521,10 @@
         <v>61</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D163" s="2"/>
     </row>
@@ -4528,10 +4533,10 @@
         <v>61</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D164" s="2"/>
     </row>
@@ -4543,7 +4548,7 @@
         <v>34</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D165" s="2"/>
     </row>
@@ -4552,10 +4557,10 @@
         <v>61</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D166" s="2"/>
     </row>
@@ -4564,10 +4569,10 @@
         <v>61</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D167" s="2"/>
     </row>
@@ -4576,10 +4581,10 @@
         <v>61</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D168" s="2"/>
     </row>
@@ -4588,10 +4593,10 @@
         <v>61</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D169" s="2"/>
     </row>
@@ -4600,10 +4605,10 @@
         <v>61</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D170" s="2"/>
     </row>
@@ -4612,10 +4617,10 @@
         <v>61</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D171" s="2"/>
     </row>
@@ -4624,10 +4629,10 @@
         <v>61</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D172" s="2"/>
     </row>
@@ -4636,10 +4641,10 @@
         <v>61</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -4648,10 +4653,10 @@
         <v>61</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D174" s="2"/>
     </row>
@@ -4660,10 +4665,10 @@
         <v>61</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -4672,10 +4677,10 @@
         <v>61</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -4684,10 +4689,10 @@
         <v>61</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -4696,10 +4701,10 @@
         <v>61</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -4708,10 +4713,10 @@
         <v>61</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -4720,10 +4725,10 @@
         <v>61</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -4732,10 +4737,10 @@
         <v>61</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -4744,10 +4749,10 @@
         <v>61</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -4756,10 +4761,10 @@
         <v>61</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -4768,10 +4773,10 @@
         <v>61</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -4780,10 +4785,10 @@
         <v>61</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -4792,10 +4797,10 @@
         <v>61</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -4804,10 +4809,10 @@
         <v>61</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -4816,10 +4821,10 @@
         <v>61</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -4828,10 +4833,10 @@
         <v>61</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -4840,10 +4845,10 @@
         <v>61</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -4852,10 +4857,10 @@
         <v>61</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -4864,10 +4869,10 @@
         <v>61</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -4876,10 +4881,10 @@
         <v>61</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -4888,10 +4893,10 @@
         <v>61</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -4900,10 +4905,10 @@
         <v>61</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -4912,10 +4917,10 @@
         <v>61</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -4924,10 +4929,10 @@
         <v>61</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -4936,10 +4941,10 @@
         <v>61</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -4948,10 +4953,10 @@
         <v>61</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -4960,10 +4965,10 @@
         <v>61</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -4972,10 +4977,10 @@
         <v>61</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -4984,10 +4989,10 @@
         <v>61</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -4996,10 +5001,10 @@
         <v>61</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5008,10 +5013,10 @@
         <v>61</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -5020,10 +5025,10 @@
         <v>61</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -5032,10 +5037,10 @@
         <v>61</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -5044,10 +5049,10 @@
         <v>61</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -5056,10 +5061,10 @@
         <v>61</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5068,10 +5073,10 @@
         <v>61</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5080,10 +5085,10 @@
         <v>61</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5092,10 +5097,10 @@
         <v>61</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5104,10 +5109,10 @@
         <v>61</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5116,10 +5121,10 @@
         <v>61</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5128,10 +5133,10 @@
         <v>61</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5140,10 +5145,10 @@
         <v>61</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5152,10 +5157,10 @@
         <v>61</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5164,10 +5169,10 @@
         <v>61</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5176,10 +5181,10 @@
         <v>61</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5188,10 +5193,10 @@
         <v>61</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5200,10 +5205,10 @@
         <v>61</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5212,10 +5217,10 @@
         <v>61</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -5224,10 +5229,10 @@
         <v>61</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -5236,10 +5241,10 @@
         <v>61</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -5248,10 +5253,10 @@
         <v>61</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -5260,10 +5265,10 @@
         <v>61</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -5272,10 +5277,10 @@
         <v>61</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -5284,10 +5289,10 @@
         <v>61</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -5296,10 +5301,10 @@
         <v>61</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -5308,10 +5313,10 @@
         <v>61</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -5320,10 +5325,10 @@
         <v>61</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -5332,10 +5337,10 @@
         <v>61</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -5344,10 +5349,10 @@
         <v>61</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -5356,10 +5361,10 @@
         <v>61</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -5368,10 +5373,10 @@
         <v>61</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -5380,10 +5385,10 @@
         <v>61</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -5392,10 +5397,10 @@
         <v>61</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -5404,10 +5409,10 @@
         <v>61</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -5416,10 +5421,10 @@
         <v>61</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -5428,10 +5433,10 @@
         <v>61</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -5440,10 +5445,10 @@
         <v>61</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -5452,10 +5457,10 @@
         <v>61</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -5464,10 +5469,10 @@
         <v>61</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -5476,10 +5481,10 @@
         <v>61</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -5488,10 +5493,10 @@
         <v>61</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -5500,10 +5505,10 @@
         <v>61</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -5512,10 +5517,10 @@
         <v>61</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -5524,10 +5529,10 @@
         <v>61</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -5536,10 +5541,10 @@
         <v>61</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -5548,10 +5553,10 @@
         <v>61</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -5560,10 +5565,10 @@
         <v>61</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -5572,10 +5577,10 @@
         <v>61</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -5584,10 +5589,10 @@
         <v>61</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -5596,10 +5601,10 @@
         <v>61</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -5608,10 +5613,10 @@
         <v>61</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -5620,10 +5625,10 @@
         <v>61</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -5632,10 +5637,10 @@
         <v>61</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -5644,10 +5649,10 @@
         <v>61</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -5656,10 +5661,10 @@
         <v>61</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -5668,10 +5673,10 @@
         <v>61</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -5680,10 +5685,10 @@
         <v>61</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -5692,10 +5697,10 @@
         <v>61</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -5704,10 +5709,10 @@
         <v>61</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -5716,10 +5721,10 @@
         <v>61</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -5728,10 +5733,10 @@
         <v>61</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -5740,10 +5745,10 @@
         <v>61</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -5752,10 +5757,10 @@
         <v>61</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -5764,10 +5769,10 @@
         <v>61</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -5776,10 +5781,10 @@
         <v>61</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -5788,10 +5793,10 @@
         <v>61</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -5800,10 +5805,10 @@
         <v>61</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -5812,10 +5817,10 @@
         <v>61</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -5824,13 +5829,13 @@
         <v>61</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D272" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="273">
@@ -5838,10 +5843,10 @@
         <v>61</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -5850,10 +5855,10 @@
         <v>61</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -5862,10 +5867,10 @@
         <v>61</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D275" s="2"/>
     </row>
@@ -5874,10 +5879,10 @@
         <v>61</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -5886,10 +5891,10 @@
         <v>61</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -5898,10 +5903,10 @@
         <v>61</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -5910,10 +5915,10 @@
         <v>61</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -5922,10 +5927,10 @@
         <v>61</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -5934,10 +5939,10 @@
         <v>61</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -5946,10 +5951,10 @@
         <v>61</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -5958,13 +5963,13 @@
         <v>61</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D283" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="284">
@@ -5972,10 +5977,10 @@
         <v>61</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -5984,10 +5989,10 @@
         <v>61</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -5996,10 +6001,10 @@
         <v>61</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6008,10 +6013,10 @@
         <v>61</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6020,10 +6025,10 @@
         <v>61</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6032,10 +6037,10 @@
         <v>61</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6044,10 +6049,10 @@
         <v>61</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6056,10 +6061,10 @@
         <v>61</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6068,10 +6073,10 @@
         <v>61</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6080,10 +6085,10 @@
         <v>61</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6092,10 +6097,10 @@
         <v>61</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6104,10 +6109,10 @@
         <v>61</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6116,10 +6121,10 @@
         <v>61</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6128,10 +6133,10 @@
         <v>61</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6140,10 +6145,10 @@
         <v>61</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6152,10 +6157,10 @@
         <v>61</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6164,10 +6169,10 @@
         <v>61</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6176,10 +6181,10 @@
         <v>61</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6188,10 +6193,10 @@
         <v>61</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6200,10 +6205,10 @@
         <v>61</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6212,10 +6217,10 @@
         <v>61</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -6224,10 +6229,10 @@
         <v>61</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -6236,10 +6241,10 @@
         <v>61</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -6248,10 +6253,10 @@
         <v>61</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -6260,10 +6265,10 @@
         <v>61</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -6272,10 +6277,10 @@
         <v>61</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -6284,13 +6289,13 @@
         <v>61</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D310" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="311">
@@ -6298,13 +6303,13 @@
         <v>61</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D311" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="312">
@@ -6312,10 +6317,10 @@
         <v>61</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -6324,10 +6329,10 @@
         <v>61</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -6336,10 +6341,10 @@
         <v>61</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -6348,10 +6353,10 @@
         <v>61</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -6360,10 +6365,10 @@
         <v>61</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -6372,10 +6377,10 @@
         <v>61</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -6384,13 +6389,13 @@
         <v>61</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D318" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="319">
@@ -6398,13 +6403,13 @@
         <v>61</v>
       </c>
       <c r="B319" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C319" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="D319" t="s" s="2">
         <v>700</v>
-      </c>
-      <c r="C319" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="D319" t="s" s="2">
-        <v>699</v>
       </c>
     </row>
     <row r="320">
@@ -6412,13 +6417,13 @@
         <v>61</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D320" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="321">
@@ -6426,10 +6431,10 @@
         <v>61</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -6438,13 +6443,13 @@
         <v>61</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D322" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="323">
@@ -6452,13 +6457,13 @@
         <v>61</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D323" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
